--- a/ТРПО.xlsx
+++ b/ТРПО.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vaces\Desktop\programm\course_forth\TRPO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Temp\ispp31\ТРПО 02.01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD14C79-0787-4FA3-B10C-6DB1319C8569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9195" yWindow="2520" windowWidth="18750" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9195" yWindow="2520" windowWidth="18750" windowHeight="13680"/>
   </bookViews>
   <sheets>
     <sheet name="Лабораторные" sheetId="1" r:id="rId1"/>
     <sheet name="Практические" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="14">
   <si>
     <t>№</t>
   </si>
@@ -76,12 +75,18 @@
   </si>
   <si>
     <t>Сделано</t>
+  </si>
+  <si>
+    <t>тут хватит</t>
+  </si>
+  <si>
+    <t>не хватит</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -528,7 +533,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -571,7 +576,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>6</v>
@@ -587,7 +592,7 @@
       </c>
       <c r="G2" s="9">
         <f t="shared" ref="G2:G6" si="0">COUNTIF(B2:F2,"!")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="6">
         <f t="shared" ref="H2:H6" si="1">COUNTIF(B2:F2,"+")</f>
@@ -596,7 +601,9 @@
       <c r="I2" s="6">
         <v>5</v>
       </c>
-      <c r="J2" s="11"/>
+      <c r="J2" s="11" t="s">
+        <v>13</v>
+      </c>
       <c r="L2" s="3" t="s">
         <v>5</v>
       </c>
@@ -609,13 +616,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>6</v>
@@ -625,7 +632,7 @@
       </c>
       <c r="G3" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" s="6">
         <f t="shared" si="1"/>
@@ -634,7 +641,9 @@
       <c r="I3" s="6">
         <v>5</v>
       </c>
-      <c r="J3" s="11"/>
+      <c r="J3" s="11" t="s">
+        <v>12</v>
+      </c>
       <c r="L3" s="4" t="s">
         <v>6</v>
       </c>
@@ -717,23 +726,23 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G6" s="9">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" s="6">
         <f t="shared" si="1"/>
@@ -765,7 +774,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/ТРПО.xlsx
+++ b/ТРПО.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="9195" yWindow="2520" windowWidth="18750" windowHeight="13680"/>
+    <workbookView xWindow="9195" yWindow="2520" windowWidth="18750" windowHeight="13680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Лабораторные" sheetId="1" r:id="rId1"/>
@@ -579,10 +579,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>6</v>
@@ -592,7 +592,7 @@
       </c>
       <c r="G2" s="9">
         <f t="shared" ref="G2:G6" si="0">COUNTIF(B2:F2,"!")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" s="6">
         <f t="shared" ref="H2:H6" si="1">COUNTIF(B2:F2,"+")</f>

--- a/ТРПО.xlsx
+++ b/ТРПО.xlsx
@@ -909,23 +909,23 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G5" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" s="6">
         <v>5</v>

--- a/ТРПО.xlsx
+++ b/ТРПО.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="9195" yWindow="2520" windowWidth="18750" windowHeight="13680" activeTab="1"/>
+    <workbookView xWindow="9195" yWindow="2520" windowWidth="18750" windowHeight="13680"/>
   </bookViews>
   <sheets>
     <sheet name="Лабораторные" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="13">
   <si>
     <t>№</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>тут хватит</t>
-  </si>
-  <si>
-    <t>не хватит</t>
   </si>
 </sst>
 </file>
@@ -96,7 +93,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -124,6 +121,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -168,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -204,7 +213,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -551,13 +567,13 @@
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
       <c r="G1" s="10" t="s">
         <v>11</v>
       </c>
@@ -602,7 +618,7 @@
         <v>5</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>5</v>
@@ -775,34 +791,38 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="12" t="s">
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -821,22 +841,26 @@
       <c r="F2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="9">
+        <f t="shared" ref="G2:G5" si="0">COUNTIF(B2:F2,"!")</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="7">
         <f>COUNTIF(B2:F2,"+")</f>
         <v>0</v>
       </c>
-      <c r="H2" s="6">
-        <v>5</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="K2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="I2" s="6">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="L2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -855,22 +879,26 @@
       <c r="F3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="7">
-        <f t="shared" ref="G3:G5" si="0">COUNTIF(B3:F3,"+")</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="6">
-        <v>5</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="K3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="G3" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H3" s="7">
+        <f t="shared" ref="H3:H5" si="1">COUNTIF(B3:F3,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="6">
+        <v>5</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="L3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -889,22 +917,26 @@
       <c r="F4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H4" s="6">
-        <v>5</v>
-      </c>
-      <c r="I4" s="1"/>
-      <c r="K4" s="5" t="s">
+      <c r="H4" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="6">
+        <v>5</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="L4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -923,14 +955,18 @@
       <c r="F5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="17">
         <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H5" s="17">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="H5" s="6">
-        <v>5</v>
-      </c>
-      <c r="I5" s="1"/>
+      <c r="I5" s="17">
+        <v>5</v>
+      </c>
+      <c r="J5" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -948,5 +984,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>